--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/KENTUCKY_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/KENTUCKY_2021.xlsx
@@ -1579,7 +1579,7 @@
         <v>32</v>
       </c>
       <c r="D68">
-        <v>0.009575104727707959</v>
+        <v>0.009575104727707961</v>
       </c>
     </row>
     <row r="69">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C90">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C185">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C192">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C428">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C479">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C500">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C501">
